--- a/branches/dependabot/github_actions/dev/actions-63cfa41bca/CodeSystem-mii-cs-dokument-nlp-processing-status.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-63cfa41bca/CodeSystem-mii-cs-dokument-nlp-processing-status.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T09:23:50+00:00</t>
+    <t>2026-09-14T09:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
